--- a/Codes_2025/Trial 3/Trial3_RF_Followers_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_RF_Followers_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,10 +473,10 @@
         <v>5.93</v>
       </c>
       <c r="D2" t="n">
-        <v>7.824163270969939</v>
+        <v>8.652065756948533</v>
       </c>
       <c r="E2" t="n">
-        <v>1.89416327096994</v>
+        <v>2.722065756948533</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -497,10 +497,10 @@
         <v>2.64</v>
       </c>
       <c r="D3" t="n">
-        <v>6.557804204896236</v>
+        <v>6.402511310368157</v>
       </c>
       <c r="E3" t="n">
-        <v>3.917804204896236</v>
+        <v>3.762511310368156</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -521,10 +521,10 @@
         <v>10.68</v>
       </c>
       <c r="D4" t="n">
-        <v>7.279705897252093</v>
+        <v>8.004752453888461</v>
       </c>
       <c r="E4" t="n">
-        <v>3.400294102747905</v>
+        <v>2.675247546111537</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -545,10 +545,10 @@
         <v>7.740000000000002</v>
       </c>
       <c r="D5" t="n">
-        <v>7.569913360227198</v>
+        <v>9.648830689089339</v>
       </c>
       <c r="E5" t="n">
-        <v>0.170086639772804</v>
+        <v>1.908830689089337</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -559,20 +559,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>37.81</v>
+        <v>19.89</v>
       </c>
       <c r="D6" t="n">
-        <v>12.64270450317586</v>
+        <v>8.572974494290593</v>
       </c>
       <c r="E6" t="n">
-        <v>25.16729549682414</v>
+        <v>11.3170255057094</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -583,20 +583,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>6.81</v>
+        <v>8.050000000000002</v>
       </c>
       <c r="D7" t="n">
-        <v>13.06328341903846</v>
+        <v>8.743907802926747</v>
       </c>
       <c r="E7" t="n">
-        <v>6.253283419038461</v>
+        <v>0.6939078029267449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -607,20 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>19.89</v>
+        <v>7.989999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>8.438191198774897</v>
+        <v>10.51562490231687</v>
       </c>
       <c r="E8" t="n">
-        <v>11.4518088012251</v>
+        <v>2.525624902316873</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -631,20 +631,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>8.050000000000002</v>
+        <v>28.09</v>
       </c>
       <c r="D9" t="n">
-        <v>8.863016485141886</v>
+        <v>9.484499262543537</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8130164851418833</v>
+        <v>18.60550073745646</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -655,20 +655,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>7.989999999999999</v>
+        <v>33.88</v>
       </c>
       <c r="D10" t="n">
-        <v>8.377494649239585</v>
+        <v>20.16107760173882</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3874946492395859</v>
+        <v>13.71892239826118</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -679,20 +679,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>28.09</v>
+        <v>5.56</v>
       </c>
       <c r="D11" t="n">
-        <v>8.110685115619924</v>
+        <v>8.438267704882097</v>
       </c>
       <c r="E11" t="n">
-        <v>19.97931488438007</v>
+        <v>2.878267704882098</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -703,94 +703,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>33.88</v>
+        <v>11.6</v>
       </c>
       <c r="D12" t="n">
-        <v>17.91808863673057</v>
+        <v>9.484499262543537</v>
       </c>
       <c r="E12" t="n">
-        <v>15.96191136326944</v>
+        <v>2.115500737456465</v>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C13" t="n">
-        <v>24.26000000000001</v>
-      </c>
-      <c r="D13" t="n">
-        <v>13.86157849245398</v>
-      </c>
-      <c r="E13" t="n">
-        <v>10.39842150754603</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7.040291607509832</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.480291607509832</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C15" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>8.347712280069764</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3.252287719930237</v>
-      </c>
-      <c r="F15" t="inlineStr">
         <is>
           <t>Followers</t>
         </is>
